--- a/experiment/HAT+CNN_2CH_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/HAT+CNN_2CH_bestx4/Test/results-Set14/Set14.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.2</v>
+        <v>26.23</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7579</v>
+        <v>0.7584</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.36</v>
+        <v>25.34</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6364</v>
+        <v>0.6353</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.29</v>
+        <v>26.26</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5792</v>
+        <v>0.5777</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.54</v>
+        <v>23.57</v>
       </c>
       <c r="C6" t="n">
-        <v>0.74</v>
+        <v>0.7403</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.95</v>
+        <v>32.96</v>
       </c>
       <c r="C7" t="n">
-        <v>0.796</v>
+        <v>0.7962</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.42</v>
+        <v>28.43</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8243</v>
+        <v>0.8246</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.7</v>
+        <v>33.73</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9203</v>
+        <v>0.9201</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.59</v>
+        <v>32.64</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8661</v>
+        <v>0.8666</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.35</v>
+        <v>27.37</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7504</v>
+        <v>0.7506</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.13</v>
+        <v>33.15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9458</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.37</v>
+        <v>34.36</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8812</v>
+        <v>0.8811</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.8</v>
+        <v>26.85</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9522</v>
+        <v>0.9525</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.26</v>
+        <v>27.32</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7784</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.64</v>
+        <v>28.66</v>
       </c>
       <c r="C16" t="n">
         <v>0.7831</v>
